--- a/Battery_Capacity/Battery_Capacity.xlsx
+++ b/Battery_Capacity/Battery_Capacity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Battery_Capacity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{B39C7B50-4E94-4FA5-9D43-E848027EAA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F167B64-A276-4F41-8E43-464F22E3454D}"/>
+  <xr:revisionPtr revIDLastSave="441" documentId="8_{B39C7B50-4E94-4FA5-9D43-E848027EAA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{034F3716-F327-4D2E-AFC0-17DB0E13D088}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B5">
         <f>Pack_Count*5*11.1*3600*UNC_Batt_Cap</f>
-        <v>455544</v>
+        <v>599400</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -546,7 +546,7 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>

--- a/Battery_Capacity/Battery_Capacity.xlsx
+++ b/Battery_Capacity/Battery_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Battery_Capacity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5235" documentId="8_{B39C7B50-4E94-4FA5-9D43-E848027EAA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBB3E1CD-261D-4732-B8D4-4397DF14AF8E}"/>
+  <xr:revisionPtr revIDLastSave="8484" documentId="8_{B39C7B50-4E94-4FA5-9D43-E848027EAA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BF0D927-C860-46B1-BA5F-15E2C0053196}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
   </bookViews>
@@ -487,7 +487,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -499,7 +499,7 @@
       </c>
       <c r="B4">
         <f>Pack_Count*3</f>
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -511,7 +511,7 @@
       </c>
       <c r="B5">
         <f>Pack_Count*5*11.1*3600*UNC_Batt_Cap</f>
-        <v>455544</v>
+        <v>1998000</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -526,7 +526,7 @@
       </c>
       <c r="B6">
         <f>Pack_Count*3*69</f>
-        <v>621</v>
+        <v>2070</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="B7">
         <f>3.15*3*B3</f>
-        <v>28.349999999999998</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -546,7 +546,7 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>

--- a/Battery_Capacity/Battery_Capacity.xlsx
+++ b/Battery_Capacity/Battery_Capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Battery_Capacity/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Battery_Capacity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="8_{B39C7B50-4E94-4FA5-9D43-E848027EAA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F18F8C4-16CF-472E-82B7-67978A0BA908}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0E6504C-926A-4EC1-9E11-DCF279F11CB0}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
+    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <definedName name="Cell_Weight">Sheet1!$B$6</definedName>
     <definedName name="Pack_Count">Sheet1!$B$3</definedName>
     <definedName name="UNC_Batt_Cap">Sheet1!$B$9</definedName>
+    <definedName name="UNC_Batt_Cost">Sheet1!$B$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>Battery Capacity</t>
   </si>
@@ -87,6 +88,12 @@
   </si>
   <si>
     <t>% Battery Carged</t>
+  </si>
+  <si>
+    <t>UNC_Batt_Cost</t>
+  </si>
+  <si>
+    <t>% Batt Cost fluctuation</t>
   </si>
 </sst>
 </file>
@@ -139,6 +146,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -458,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41EFFC3E-008D-46FD-8D1C-98A380E1D447}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -533,7 +544,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <f>3.15*3*B3</f>
+        <f>3.15*3*B3*B10</f>
         <v>28.349999999999998</v>
       </c>
     </row>
@@ -546,6 +557,17 @@
       </c>
       <c r="C9" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Battery_Capacity/Battery_Capacity.xlsx
+++ b/Battery_Capacity/Battery_Capacity.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Battery_Capacity/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Battery_Capacity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0E6504C-926A-4EC1-9E11-DCF279F11CB0}"/>
+  <xr:revisionPtr revIDLastSave="18173" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F309C7A4-76F3-45CE-9884-A1CC66448F22}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5">
         <f>Pack_Count*5*11.1*3600*UNC_Batt_Cap</f>
-        <v>455544</v>
+        <v>583906.56954386272</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="B7">
         <f>3.15*3*B3*B10</f>
-        <v>28.349999999999998</v>
+        <v>29.069588798896493</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -553,7 +553,7 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.76</v>
+        <v>0.97415176767411205</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -564,7 +564,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>1.0253823209487301</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>

--- a/Battery_Capacity/Battery_Capacity.xlsx
+++ b/Battery_Capacity/Battery_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Battery_Capacity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18173" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F309C7A4-76F3-45CE-9884-A1CC66448F22}"/>
+  <xr:revisionPtr revIDLastSave="20489" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4B9C968-C8D4-4F22-B316-18D24618117B}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <definedName name="UNC_Batt_Cap">Sheet1!$B$9</definedName>
     <definedName name="UNC_Batt_Cost">Sheet1!$B$10</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5">
         <f>Pack_Count*5*11.1*3600*UNC_Batt_Cap</f>
-        <v>583906.56954386272</v>
+        <v>544264.60667248687</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="B7">
         <f>3.15*3*B3*B10</f>
-        <v>29.069588798896493</v>
+        <v>28.699178325505883</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -553,7 +553,7 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.97415176767411205</v>
+        <v>0.90801569348095901</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -564,7 +564,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>1.0253823209487301</v>
+        <v>1.01231669578504</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>

--- a/Battery_Capacity/Battery_Capacity.xlsx
+++ b/Battery_Capacity/Battery_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Battery_Capacity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20489" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4B9C968-C8D4-4F22-B316-18D24618117B}"/>
+  <xr:revisionPtr revIDLastSave="20579" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF4A5745-F50D-4744-A74B-D6E6D7F4855D}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
   </bookViews>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5">
         <f>Pack_Count*5*11.1*3600*UNC_Batt_Cap</f>
-        <v>544264.60667248687</v>
+        <v>59084.818422765769</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="B7">
         <f>3.15*3*B3*B10</f>
-        <v>28.699178325505883</v>
+        <v>3.0735752822820297</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -553,7 +553,7 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.90801569348095901</v>
+        <v>9.8573270641918204E-2</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -564,7 +564,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>1.01231669578504</v>
+        <v>0.10841535387238201</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>

--- a/Battery_Capacity/Battery_Capacity.xlsx
+++ b/Battery_Capacity/Battery_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Battery_Capacity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20579" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF4A5745-F50D-4744-A74B-D6E6D7F4855D}"/>
+  <xr:revisionPtr revIDLastSave="21551" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF3D7E91-4C46-4895-8FFB-1B5EFB644867}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
   </bookViews>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5">
         <f>Pack_Count*5*11.1*3600*UNC_Batt_Cap</f>
-        <v>59084.818422765769</v>
+        <v>58273.0977554118</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="B7">
         <f>3.15*3*B3*B10</f>
-        <v>3.0735752822820297</v>
+        <v>3.4863179451803732</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -553,7 +553,7 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>9.8573270641918204E-2</v>
+        <v>9.7219048640993996E-2</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -564,7 +564,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.10841535387238201</v>
+        <v>0.122974177960507</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>

--- a/Battery_Capacity/Battery_Capacity.xlsx
+++ b/Battery_Capacity/Battery_Capacity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Battery_Capacity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21551" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF3D7E91-4C46-4895-8FFB-1B5EFB644867}"/>
+  <xr:revisionPtr revIDLastSave="24551" documentId="114_{C6D45846-3148-4081-A19D-15A1F6BD3370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CC2BB63-0D24-4EB5-86DC-6C7E32D1172B}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{21964307-0BB7-4DE0-BD23-E82C9EC81DDB}"/>
   </bookViews>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5">
         <f>Pack_Count*5*11.1*3600*UNC_Batt_Cap</f>
-        <v>58273.0977554118</v>
+        <v>63149.991064902228</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="B7">
         <f>3.15*3*B3*B10</f>
-        <v>3.4863179451803732</v>
+        <v>25.000673015324427</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -553,7 +553,7 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>9.7219048640993996E-2</v>
+        <v>0.10535534044861899</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -564,7 +564,7 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.122974177960507</v>
+        <v>0.88185795468516504</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
